--- a/data/AttributeDimension.xlsx
+++ b/data/AttributeDimension.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,9 +478,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -1086,6 +1083,174 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>401</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>体质</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>体质:提高宝宝气血上限和防御。</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>402</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>灵力</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>灵力:提高宝宝法力上限和法伤。</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>403</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>力量</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>力量:提高宝宝物伤。</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>404</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>敏捷</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>敏捷:提高宝宝出手速度。</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L22" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/AttributeDimension.xlsx
+++ b/data/AttributeDimension.xlsx
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -654,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>

--- a/data/AttributeDimension.xlsx
+++ b/data/AttributeDimension.xlsx
@@ -741,7 +741,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13">
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="20">
@@ -1155,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5</v>
+        <v>33</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
